--- a/evac_by_zip/evac_by_zip_2026-08-18.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-18.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1758,11 +1758,11 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1784,23 +1784,23 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>No named fire; Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1822,146 +1822,70 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>97830</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>Wheeler</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>97067</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Placed on a ZIP code (table above)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>3858</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1519</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>992</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Not placed on any ZIP code (unmatched)</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>172</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>274</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>Placed on a ZIP code (table above)</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n">
-        <v>3866</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>1519</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>992</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>6377</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Not placed on any ZIP code (unmatched)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
-        <v>172</v>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Reconciled total (matches morning report)</t>
         </is>
       </c>
-      <c r="B42" s="18" t="n">
-        <v>4038</v>
-      </c>
-      <c r="C42" s="18" t="n">
+      <c r="B40" s="18" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C40" s="18" t="n">
         <v>1580</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D40" s="18" t="n">
         <v>1033</v>
       </c>
-      <c r="E42" s="18" t="n">
-        <v>6651</v>
+      <c r="E40" s="18" t="n">
+        <v>6643</v>
       </c>
     </row>
   </sheetData>
@@ -1979,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11908,22 +11832,22 @@
     <row r="285">
       <c r="A285" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B285" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-034-A</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C285" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D285" s="26" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E285" s="25" t="inlineStr">
@@ -11933,32 +11857,32 @@
       </c>
       <c r="F285" s="25" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G285" s="25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B286" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-090-A</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C286" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D286" s="26" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E286" s="25" t="inlineStr">
@@ -11968,7 +11892,7 @@
       </c>
       <c r="F286" s="25" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G286" s="25" t="n">
@@ -11978,22 +11902,22 @@
     <row r="287">
       <c r="A287" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="B287" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C287" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D287" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E287" s="25" t="inlineStr">
@@ -12003,32 +11927,32 @@
       </c>
       <c r="F287" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G287" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B288" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-WHE-WHH-090-A</t>
         </is>
       </c>
       <c r="C288" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D288" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Wheeler</t>
         </is>
       </c>
       <c r="E288" s="25" t="inlineStr">
@@ -12038,7 +11962,7 @@
       </c>
       <c r="F288" s="25" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G288" s="25" t="n">
@@ -12048,12 +11972,12 @@
     <row r="289">
       <c r="A289" s="25" t="inlineStr">
         <is>
-          <t>97830</t>
+          <t>97864</t>
         </is>
       </c>
       <c r="B289" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-034-A</t>
+          <t>US-OR-GRA-GRN-023</t>
         </is>
       </c>
       <c r="C289" s="26" t="inlineStr">
@@ -12063,7 +11987,7 @@
       </c>
       <c r="D289" s="26" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="E289" s="25" t="inlineStr">
@@ -12073,22 +11997,22 @@
       </c>
       <c r="F289" s="25" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G289" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="25" t="inlineStr">
         <is>
-          <t>97067</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="B290" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>LDWT</t>
         </is>
       </c>
       <c r="C290" s="26" t="inlineStr">
@@ -12098,7 +12022,7 @@
       </c>
       <c r="D290" s="26" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E290" s="25" t="inlineStr">
@@ -12108,7 +12032,7 @@
       </c>
       <c r="F290" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G290" s="25" t="n">
@@ -12118,22 +12042,22 @@
     <row r="291">
       <c r="A291" s="25" t="inlineStr">
         <is>
-          <t>97874</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="B291" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-034-A</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C291" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D291" s="26" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E291" s="25" t="inlineStr">
@@ -12143,7 +12067,7 @@
       </c>
       <c r="F291" s="25" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G291" s="25" t="n">
@@ -12153,22 +12077,22 @@
     <row r="292">
       <c r="A292" s="25" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>97040</t>
         </is>
       </c>
       <c r="B292" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-023</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="C292" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D292" s="26" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E292" s="25" t="inlineStr">
@@ -12188,22 +12112,22 @@
     <row r="293">
       <c r="A293" s="25" t="inlineStr">
         <is>
-          <t>97029</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B293" s="26" t="inlineStr">
         <is>
-          <t>LDWT</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C293" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D293" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E293" s="25" t="inlineStr">
@@ -12213,120 +12137,15 @@
       </c>
       <c r="F293" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G293" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="25" t="inlineStr">
-        <is>
-          <t>97029</t>
-        </is>
-      </c>
-      <c r="B294" s="26" t="inlineStr">
-        <is>
-          <t>SBR</t>
-        </is>
-      </c>
-      <c r="C294" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D294" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E294" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F294" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G294" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="25" t="inlineStr">
-        <is>
-          <t>97040</t>
-        </is>
-      </c>
-      <c r="B295" s="26" t="inlineStr">
-        <is>
-          <t>MCR</t>
-        </is>
-      </c>
-      <c r="C295" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D295" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E295" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F295" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G295" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="25" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B296" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C296" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D296" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E296" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F296" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G296" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" ht="60" customHeight="1">
-      <c r="A298" s="27" t="inlineStr">
+    <row r="295" ht="60" customHeight="1">
+      <c r="A295" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -12334,7 +12153,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A298:G298"/>
+    <mergeCell ref="A295:G295"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
